--- a/data/trans_orig/IQ3006_MoAR-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ3006_MoAR-Provincia-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en años en la que empezaron a beber leche normal</t>
+          <t>Menores según la edad en años en la que empezaron a beber leche normal (tasa de respuesta: 32,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,0; 13,5</t>
+          <t>12,0; 14,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,12; 19,0</t>
+          <t>12,01; 18,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,48; 20,1</t>
+          <t>11,32; 20,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -697,34 +697,34 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,21; 14,45</t>
+          <t>7,83; 14,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,78; 18,7</t>
+          <t>6,75; 17,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,0; 12,88</t>
+          <t>12,0; 12,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,07; 15,57</t>
+          <t>11,28; 15,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,32; 16,91</t>
+          <t>8,94; 16,73</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -792,49 +792,49 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,31; 19,95</t>
+          <t>12,43; 20,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,27; 16,64</t>
+          <t>9,65; 17,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,48; 17,46</t>
+          <t>11,32; 17,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 12,21</t>
+          <t>4,2; 12,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,25; 18,0</t>
+          <t>12,25; 16,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,51; 17,7</t>
+          <t>12,52; 17,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,78; 16,6</t>
+          <t>9,81; 16,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,95; 15,7</t>
+          <t>11,25; 15,85</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,12 +897,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 13,4</t>
+          <t>2,38; 13,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,67; 16,74</t>
+          <t>11,38; 16,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,33; 16,62</t>
+          <t>7,92; 16,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,83; 18,42</t>
+          <t>12,42; 18,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -927,12 +927,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,15; 14,64</t>
+          <t>7,34; 14,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,61; 16,53</t>
+          <t>12,71; 16,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,12; 16,6</t>
+          <t>11,33; 16,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,26; 13,81</t>
+          <t>8,94; 13,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,43; 18,1</t>
+          <t>12,16; 17,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,0; 16,62</t>
+          <t>12,0; 16,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,59; 16,6</t>
+          <t>12,42; 16,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,29; 14,56</t>
+          <t>10,94; 14,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,0; 14,76</t>
+          <t>12,0; 14,59</t>
         </is>
       </c>
     </row>
@@ -1122,17 +1122,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,49; 14,49</t>
+          <t>9,53; 14,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,52; 13,77</t>
+          <t>8,32; 13,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,5; 14,45</t>
+          <t>6,23; 14,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1147,24 +1147,24 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,25; 15,2</t>
+          <t>7,97; 15,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,48; 15,78</t>
+          <t>10,95; 15,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,62; 12,52</t>
+          <t>7,61; 12,43</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,55; 16,27</t>
+          <t>12,6; 16,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,02; 22,96</t>
+          <t>14,03; 22,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1252,29 +1252,29 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,52; 21,17</t>
+          <t>11,09; 21,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,29; 15,03</t>
+          <t>12,3; 15,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,36; 20,46</t>
+          <t>13,37; 20,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,66; 20,7</t>
+          <t>13,54; 20,92</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,79; 17,91</t>
+          <t>12,56; 17,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,24; 18,6</t>
+          <t>13,45; 18,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,77; 13,55</t>
+          <t>9,08; 13,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,88; 15,39</t>
+          <t>9,93; 15,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,18; 18,53</t>
+          <t>14,09; 18,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,44; 13,67</t>
+          <t>11,44; 13,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,96; 15,55</t>
+          <t>11,74; 15,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,5; 17,9</t>
+          <t>14,65; 17,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,71; 12,97</t>
+          <t>10,79; 13,04</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,64; 17,24</t>
+          <t>10,5; 17,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,16; 13,94</t>
+          <t>11,28; 14,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,27; 15,34</t>
+          <t>10,26; 15,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,54; 11,69</t>
+          <t>8,44; 11,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,28; 13,45</t>
+          <t>8,53; 13,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,07; 16,07</t>
+          <t>10,66; 15,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,06; 13,66</t>
+          <t>10,16; 13,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,45; 13,21</t>
+          <t>10,53; 13,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,87; 14,38</t>
+          <t>11,04; 14,75</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1557,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12,06; 15,01</t>
+          <t>11,97; 14,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12,82; 14,89</t>
+          <t>12,79; 14,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,69; 14,33</t>
+          <t>11,92; 14,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,5; 13,45</t>
+          <t>11,4; 13,49</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,18; 14,75</t>
+          <t>12,17; 14,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,18; 13,89</t>
+          <t>11,23; 13,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,06; 13,73</t>
+          <t>12,09; 13,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12,78; 14,37</t>
+          <t>12,9; 14,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11,86; 13,65</t>
+          <t>11,85; 13,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3006_MoAR-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ3006_MoAR-Provincia-trans_orig.xlsx
@@ -682,12 +682,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,01; 18,98</t>
+          <t>12,08; 19,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,32; 20,38</t>
+          <t>11,48; 20,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -697,12 +697,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,83; 14,35</t>
+          <t>7,26; 14,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,75; 17,55</t>
+          <t>6,61; 18,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -712,12 +712,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,28; 15,57</t>
+          <t>11,27; 15,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,94; 16,73</t>
+          <t>8,66; 16,09</t>
         </is>
       </c>
     </row>
@@ -792,42 +792,42 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,43; 20,02</t>
+          <t>12,4; 20,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,65; 17,0</t>
+          <t>9,25; 16,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,32; 17,31</t>
+          <t>11,26; 17,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 12,51</t>
+          <t>3,95; 12,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,25; 16,75</t>
+          <t>12,25; 16,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,52; 17,86</t>
+          <t>12,43; 17,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,81; 16,87</t>
+          <t>9,7; 16,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,25; 15,85</t>
+          <t>11,31; 15,84</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,38; 16,75</t>
+          <t>11,38; 16,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,92; 16,61</t>
+          <t>7,71; 16,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,42; 18,15</t>
+          <t>12,83; 18,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -927,12 +927,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,34; 14,62</t>
+          <t>6,95; 14,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,71; 16,25</t>
+          <t>12,65; 16,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,33; 16,96</t>
+          <t>11,05; 16,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,94; 13,28</t>
+          <t>9,24; 13,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,16; 17,64</t>
+          <t>12,24; 18,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,0; 16,8</t>
+          <t>12,0; 16,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,42; 16,53</t>
+          <t>12,56; 16,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,94; 14,5</t>
+          <t>11,11; 14,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,0; 14,59</t>
+          <t>12,0; 14,55</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,83; 17,86</t>
+          <t>6,75; 18,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,32; 13,92</t>
+          <t>8,4; 13,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,47; 10,44</t>
+          <t>5,47; 11,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,97; 15,05</t>
+          <t>8,13; 15,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,61; 12,43</t>
+          <t>7,63; 12,49</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,6; 16,48</t>
+          <t>12,61; 16,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,03; 22,06</t>
+          <t>14,97; 22,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,09; 21,16</t>
+          <t>9,99; 20,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,3; 15,08</t>
+          <t>12,29; 14,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,54; 20,92</t>
+          <t>13,11; 20,69</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,56; 17,86</t>
+          <t>12,49; 17,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,45; 18,5</t>
+          <t>12,97; 18,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,08; 13,37</t>
+          <t>9,09; 13,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,93; 15,39</t>
+          <t>9,81; 15,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,09; 18,58</t>
+          <t>14,09; 18,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,44; 13,6</t>
+          <t>11,45; 13,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,74; 15,62</t>
+          <t>11,8; 15,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,65; 17,95</t>
+          <t>14,4; 17,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,79; 13,04</t>
+          <t>10,74; 13,07</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,5; 17,36</t>
+          <t>10,37; 17,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,28; 14,06</t>
+          <t>11,28; 14,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,26; 15,39</t>
+          <t>10,25; 15,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,44; 11,64</t>
+          <t>8,46; 11,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,53; 13,46</t>
+          <t>8,47; 13,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,66; 15,95</t>
+          <t>10,76; 15,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,16; 13,64</t>
+          <t>10,09; 13,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,53; 13,3</t>
+          <t>10,28; 13,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,04; 14,75</t>
+          <t>11,0; 14,73</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1557,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11,97; 14,86</t>
+          <t>11,93; 14,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12,79; 14,75</t>
+          <t>12,8; 14,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,92; 14,41</t>
+          <t>11,92; 14,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,4; 13,49</t>
+          <t>11,45; 13,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,17; 14,64</t>
+          <t>12,24; 14,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,23; 13,99</t>
+          <t>11,2; 13,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,09; 13,72</t>
+          <t>12,05; 13,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12,9; 14,5</t>
+          <t>12,8; 14,39</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11,85; 13,72</t>
+          <t>11,91; 13,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3006_MoAR-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ3006_MoAR-Provincia-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12,17</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10,66</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>12,5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>13,95</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>14,57</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>12,17</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,66</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,0; 14,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,08; 19,44</t>
+          <t>8,21; 14,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>6,78; 18,7</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12,0; 13,5</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>12,12; 19,0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>11,48; 20,1</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>7,26; 14,33</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,61; 18,2</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,0; 12,89</t>
+          <t>12,0; 12,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,27; 15,82</t>
+          <t>11,07; 15,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,66; 16,09</t>
+          <t>9,32; 16,91</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>14,04</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8,57</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13,77</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>19,37</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>15,47</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>13,62</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>14,04</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,57</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>13,77</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11,48; 17,46</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2,85; 12,21</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12,25; 18,0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>18,0; 22,0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>12,4; 20,27</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9,25; 16,64</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11,26; 17,38</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,95; 12,29</t>
+          <t>12,31; 19,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,25; 16,99</t>
+          <t>9,27; 16,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,43; 17,69</t>
+          <t>12,51; 17,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,7; 16,41</t>
+          <t>9,78; 16,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,31; 15,84</t>
+          <t>10,95; 15,7</t>
         </is>
       </c>
     </row>
@@ -844,27 +844,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13,97</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14,69</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12,0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>8,93</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>13,69</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>12,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13,97</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14,69</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -897,12 +897,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 13,91</t>
+          <t>7,33; 16,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,38; 16,13</t>
+          <t>12,83; 18,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,71; 16,62</t>
+          <t>2,3; 13,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,83; 18,52</t>
+          <t>11,67; 16,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -927,12 +927,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,95; 14,48</t>
+          <t>7,15; 14,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,65; 16,4</t>
+          <t>12,61; 16,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14,38</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14,26</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12,0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>13,64</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>11,85</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>13,57</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14,38</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,26</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,05; 16,8</t>
+          <t>12,43; 18,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,24; 13,84</t>
+          <t>12,0; 16,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11,12; 16,6</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9,26; 13,81</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>12,0; 18,0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>12,24; 18,08</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>12,0; 16,64</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,56; 16,42</t>
+          <t>12,59; 16,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,11; 14,63</t>
+          <t>11,29; 14,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,0; 14,55</t>
+          <t>12,0; 14,76</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11,32</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16,51</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7,53</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>11,28</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>12,0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>11,46</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11,32</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>16,51</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,53</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,75; 18,17</t>
+          <t>6,5; 14,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,53; 14,48</t>
+          <t>13,5; 18,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,4; 13,98</t>
+          <t>5,47; 10,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,23; 14,45</t>
+          <t>6,83; 17,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,5; 18,0</t>
+          <t>9,49; 14,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,47; 11,2</t>
+          <t>8,52; 13,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,13; 15,08</t>
+          <t>8,25; 15,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,95; 15,77</t>
+          <t>11,48; 15,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,63; 12,49</t>
+          <t>7,62; 12,52</t>
         </is>
       </c>
     </row>
@@ -1174,32 +1174,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>12,0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16,96</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16,36</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>14,38</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>14,61</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>18,99</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12,0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>16,96</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>16,36</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,61; 16,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>12,0; 22,43</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>10,52; 21,17</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>12,55; 16,27</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>14,0; 15,0</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>14,97; 22,96</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>12,0; 22,43</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,99; 20,91</t>
+          <t>14,02; 22,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,29; 14,81</t>
+          <t>12,29; 15,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,37; 20,46</t>
+          <t>13,36; 20,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,11; 20,69</t>
+          <t>13,66; 20,7</t>
         </is>
       </c>
     </row>
@@ -1284,32 +1284,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>12,41</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16,17</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12,28</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>14,8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>16,28</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>11,43</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>12,41</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>16,17</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12,28</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,49; 17,97</t>
+          <t>9,88; 15,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,97; 18,5</t>
+          <t>14,18; 18,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,09; 13,43</t>
+          <t>11,44; 13,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,81; 15,16</t>
+          <t>12,79; 17,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,09; 18,5</t>
+          <t>13,24; 18,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,45; 13,79</t>
+          <t>8,77; 13,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,8; 15,74</t>
+          <t>11,96; 15,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,4; 17,84</t>
+          <t>14,5; 17,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,74; 13,07</t>
+          <t>10,71; 12,97</t>
         </is>
       </c>
     </row>
@@ -1394,32 +1394,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>10,44</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11,13</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>12,84</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>14,05</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>12,41</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>11,84</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>10,44</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>11,13</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>12,84</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,37; 17,29</t>
+          <t>8,54; 11,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,28; 14,15</t>
+          <t>8,28; 13,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,25; 15,49</t>
+          <t>11,07; 16,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,46; 11,75</t>
+          <t>10,64; 17,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,47; 13,27</t>
+          <t>11,16; 13,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,76; 15,71</t>
+          <t>10,27; 15,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,09; 13,62</t>
+          <t>10,06; 13,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,28; 13,09</t>
+          <t>10,45; 13,21</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,0; 14,73</t>
+          <t>10,87; 14,38</t>
         </is>
       </c>
     </row>
@@ -1504,32 +1504,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>12,48</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>13,5</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>12,51</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>13,47</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>13,68</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>13,1</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>12,48</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>13,5</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>12,51</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1557,47 +1557,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11,93; 14,9</t>
+          <t>11,5; 13,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12,8; 14,81</t>
+          <t>12,18; 14,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,92; 14,53</t>
+          <t>11,18; 13,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,45; 13,46</t>
+          <t>12,06; 15,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,24; 14,58</t>
+          <t>12,82; 14,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,2; 13,97</t>
+          <t>11,69; 14,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,05; 13,72</t>
+          <t>12,06; 13,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12,8; 14,39</t>
+          <t>12,78; 14,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11,91; 13,83</t>
+          <t>11,86; 13,65</t>
         </is>
       </c>
     </row>
